--- a/basedatos_partidas/salida/descompuestos/09.12.03.020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/09.12.03.020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -541,105 +541,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-DOM-DIMMER</t>
+          <t>MT-CABLE-8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Módulo regulador (dimmer) para atenuación de iluminación, compatible con la central domótica.</t>
+          <t>Conductor de cobre THW calibre 8 AWG para acometidas y circuitos de fuerza.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>1.45</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-CABLE-8</t>
+          <t>MT-ELE-CAJA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Conductor de cobre THW calibre 8 AWG para acometidas y circuitos de fuerza.</t>
+          <t>Caja de paso o de mecanismo, metálica o de PVC, para empotrar.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.17</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MT-ELE-CAJA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Caja de paso o de mecanismo, metálica o de PVC, para empotrar.</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal materiales:</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Mano de obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MO-OF1-ELE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Oficial de 1ª electricista.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal materiales:</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48.27</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>Mano de obra</t>
-        </is>
+      <c r="G14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MO-OF1-ELE</t>
+          <t>MO-AYU</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -649,100 +649,74 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª electricista.</t>
+          <t>Ayudante.</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal mano de obra:</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MO-AYU</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Ayudante.</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal mano de obra:</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
+      <c r="G18" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3):</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="5" t="n">
-        <v>55.72</v>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="5" t="n">
+        <v>10.27</v>
       </c>
     </row>
   </sheetData>
